--- a/data_generation/07_soil_degradation/soil_degradation_EFSA_PEC_soil_luel_additional_ai.xlsx
+++ b/data_generation/07_soil_degradation/soil_degradation_EFSA_PEC_soil_luel_additional_ai.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Data-Work\41_AssessmentPPP-RE\412.34_Projekte\054_derappp\05_Daten\Input\07_soil_degradation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7134A3AF-9625-409F-ADEA-4F41853615B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A6A1019-254D-4E5D-8D85-0DA6AF975297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-29085" yWindow="4545" windowWidth="28800" windowHeight="6705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle2" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="125">
   <si>
     <t>SFO</t>
   </si>
@@ -386,6 +386,36 @@
   </si>
   <si>
     <t>No DT50 required for PEC soil in 2015 EFSA conclusion, see p44, worst-case lab DT50 is from study at 10°C</t>
+  </si>
+  <si>
+    <t>Propamocarb</t>
+  </si>
+  <si>
+    <t>j.efsa.2015.3973</t>
+  </si>
+  <si>
+    <t>no degradation considered</t>
+  </si>
+  <si>
+    <t>j.efsa.2006.78r</t>
+  </si>
+  <si>
+    <t>j.efsa.2014.3913</t>
+  </si>
+  <si>
+    <t>EFSA PECsw</t>
+  </si>
+  <si>
+    <t>mean (input for PEC sw)</t>
+  </si>
+  <si>
+    <t>median (input for PEC sw)</t>
+  </si>
+  <si>
+    <t>Halauxifen-methyl</t>
+  </si>
+  <si>
+    <t>Ferric phosphate</t>
   </si>
 </sst>
 </file>
@@ -741,21 +771,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44ABC253-0668-4FE2-BC14-84FC263B038A}">
-  <dimension ref="A1:Q16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="24" style="3" customWidth="1"/>
-    <col min="3" max="4" width="8.42578125" customWidth="1"/>
-    <col min="5" max="7" width="6.85546875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="3" customWidth="1"/>
-    <col min="9" max="10" width="6.85546875" style="3" customWidth="1"/>
+    <col min="3" max="4" width="8.453125" customWidth="1"/>
+    <col min="5" max="7" width="6.81640625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="9.1796875" style="3" customWidth="1"/>
+    <col min="9" max="10" width="6.81640625" style="3" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" customWidth="1"/>
-    <col min="14" max="14" width="33.140625" customWidth="1"/>
+    <col min="12" max="12" width="8.1796875" customWidth="1"/>
+    <col min="14" max="14" width="33.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="2" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -808,7 +838,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>71</v>
       </c>
@@ -837,7 +867,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>86</v>
       </c>
@@ -866,7 +896,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -898,7 +928,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -927,7 +957,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>73</v>
       </c>
@@ -959,7 +989,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>85</v>
       </c>
@@ -988,7 +1018,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -1017,7 +1047,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>90</v>
       </c>
@@ -1046,7 +1076,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>93</v>
       </c>
@@ -1075,7 +1105,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>94</v>
       </c>
@@ -1104,7 +1134,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>96</v>
       </c>
@@ -1133,7 +1163,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>97</v>
       </c>
@@ -1162,7 +1192,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>98</v>
       </c>
@@ -1197,7 +1227,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>99</v>
       </c>
@@ -1236,7 +1266,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>100</v>
       </c>
@@ -1271,6 +1301,157 @@
         <v>108</v>
       </c>
       <c r="P16" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="3">
+        <v>136</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="L17" s="3">
+        <v>60</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18">
+        <v>10.19</v>
+      </c>
+      <c r="D18" t="s">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="L18">
+        <v>64</v>
+      </c>
+      <c r="M18" t="s">
+        <v>33</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O18" t="s">
+        <v>122</v>
+      </c>
+      <c r="P18" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="3">
+        <v>43</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="L19" s="3">
+        <v>56</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="P19" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C20">
+        <v>20</v>
+      </c>
+      <c r="D20" t="s">
+        <v>0</v>
+      </c>
+      <c r="K20" t="s">
+        <v>119</v>
+      </c>
+      <c r="L20">
+        <v>56</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="P20" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+      <c r="K21" t="s">
+        <v>116</v>
+      </c>
+      <c r="L21">
+        <v>34</v>
+      </c>
+      <c r="M21" t="s">
+        <v>33</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O21" t="s">
+        <v>117</v>
+      </c>
+      <c r="P21" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1284,9 +1465,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EAD96ED-6947-4032-A468-AE450047F46C}">
   <dimension ref="A1:B26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>41</v>
       </c>
@@ -1294,7 +1475,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>43</v>
       </c>
@@ -1302,7 +1483,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -1310,7 +1491,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>47</v>
       </c>
@@ -1318,7 +1499,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>49</v>
       </c>
@@ -1326,7 +1507,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -1334,7 +1515,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1342,7 +1523,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1350,7 +1531,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -1358,7 +1539,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -1366,7 +1547,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1374,7 +1555,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1382,7 +1563,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1390,7 +1571,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -1398,7 +1579,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -1406,7 +1587,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -1414,7 +1595,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -1422,7 +1603,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1430,7 +1611,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -1438,7 +1619,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -1446,7 +1627,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -1454,7 +1635,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>2</v>
       </c>
@@ -1462,7 +1643,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>13</v>
       </c>
@@ -1470,7 +1651,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>67</v>
       </c>
@@ -1478,7 +1659,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>68</v>
       </c>
@@ -1486,7 +1667,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>4</v>
       </c>
